--- a/human_resources_forms/010_team_leadership_assessment_form--human_resources_forms.xlsx
+++ b/human_resources_forms/010_team_leadership_assessment_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1</t>
+          <t>team_leadership_style</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>What is the team's leadership style?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_1</t>
+          <t>team_dynamics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leadership Style</t>
+          <t>How do team members collaborate with each other?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_2</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team Work</t>
+          <t>List the team members</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2</t>
+          <t>leadership_style</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>What leadership style works best for this team?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_1</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Leadership Style</t>
+          <t>How do team members work together?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,20 +630,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_2</t>
+          <t>team_strengths_and_challenges</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Team Work</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are the team's strengths and challenges?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide a brief description</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -658,39 +662,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_3</t>
+          <t>influential_member</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Team Members</t>
+          <t>Who do you think is the most influential team member?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>team_leadership_assessment_form_page_3_question_1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Leadership Style</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -707,10 +688,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -735,408 +716,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_choices</t>
+          <t>team_leadership_style_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>autocratic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Autocratic</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_choices</t>
+          <t>team_leadership_style_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>democratic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Democratic</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_choices</t>
+          <t>team_leadership_style_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>joe</t>
+          <t>laissez-faire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Laissez-faire</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_1_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>autocratic</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Autocratic</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_1_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>laissez-faire</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Laissez-faire</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_1_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>democratic</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_2_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_2_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>collaboration</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_1_question_2_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adaptability</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_choices</t>
+          <t>leadership_style_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>john</t>
+          <t>autocratic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Autocratic</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_choices</t>
+          <t>leadership_style_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>jane</t>
+          <t>laissez-faire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Laissez-faire</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_choices</t>
+          <t>leadership_style_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>joe</t>
+          <t>democratic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Democratic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_1_choices</t>
+          <t>teamwork_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>autocratic</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Autocratic</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_1_choices</t>
+          <t>teamwork_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>laissez-faire</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Laissez-faire</t>
+          <t>Collaboration</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_1_choices</t>
+          <t>teamwork_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>democratic</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Democratic</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_2_choices</t>
+          <t>influential_member_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>John</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_2_choices</t>
+          <t>influential_member_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>collaboration</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>team_leadership_assessment_form_page_2_question_2_choices</t>
+          <t>influential_member_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Adaptability</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>team_leadership_assessment_form_page_3_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>john</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>John</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>team_leadership_assessment_form_page_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>jane</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>team_leadership_assessment_form_page_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>joe</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>Joe</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>team_leadership_assessment_form_page_3_question_1_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>autocratic</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Autocratic</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>team_leadership_assessment_form_page_3_question_1_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>laissez-faire</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Laissez-faire</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>team_leadership_assessment_form_page_3_question_1_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>democratic</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Democratic</t>
         </is>
       </c>
     </row>
